--- a/ZonasEscolares/excels/ICA-ICA-ICA.xlsx
+++ b/ZonasEscolares/excels/ICA-ICA-ICA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/ICA-ICA-ICA.xlsx
+++ b/ZonasEscolares/excels/ICA-ICA-ICA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>01</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-14.05492</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-75.74874</v>
-      </c>
-      <c r="I2" t="n">
-        <v>308</v>
-      </c>
-      <c r="J2" t="n">
-        <v>15</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-14.05492</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-75.74874</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>05 / JOSE MATIAS MANZANILLA</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-14.06691</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-75.72376</v>
-      </c>
-      <c r="I3" t="n">
-        <v>480</v>
-      </c>
-      <c r="J3" t="n">
-        <v>32</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-14.06691</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-75.72376</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>14 MERCEDES DIBOS DE CAMINO</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-14.07728</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-75.73369</v>
-      </c>
-      <c r="I4" t="n">
-        <v>533</v>
-      </c>
-      <c r="J4" t="n">
-        <v>26</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-14.07728</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-75.73369</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>533</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>16</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-14.05375</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-75.73603</v>
-      </c>
-      <c r="I5" t="n">
-        <v>213</v>
-      </c>
-      <c r="J5" t="n">
-        <v>10</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-14.05375</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-75.73603</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>147 / 22495 MICAELA GALINDO ROJAS DE CACERES</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-14.06688</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-75.73694</v>
-      </c>
-      <c r="I6" t="n">
-        <v>870</v>
-      </c>
-      <c r="J6" t="n">
-        <v>33</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-14.06688</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-75.73694</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>870</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>22</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-14.04609</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-75.74496000000001</v>
-      </c>
-      <c r="I7" t="n">
-        <v>209</v>
-      </c>
-      <c r="J7" t="n">
-        <v>9</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-14.04609</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-75.74496</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>22303 SANTA ROSA DE LIMA</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-14.05946</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-75.7372</v>
-      </c>
-      <c r="I8" t="n">
-        <v>659</v>
-      </c>
-      <c r="J8" t="n">
-        <v>31</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-14.05946</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-75.7372</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>132 SAGRADO CORAZON DEL NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-14.05933</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-75.73022</v>
-      </c>
-      <c r="I9" t="n">
-        <v>366</v>
-      </c>
-      <c r="J9" t="n">
-        <v>17</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-14.05933</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-75.73022</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>CABO G.C. TEODOSIO ESTEBAN FRANCO GARCIA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-14.06438</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-75.72633</v>
-      </c>
-      <c r="I10" t="n">
-        <v>949</v>
-      </c>
-      <c r="J10" t="n">
-        <v>49</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-14.06438</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-75.72633</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>22295</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-14.06683</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-75.73526</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1337</v>
-      </c>
-      <c r="J11" t="n">
-        <v>47</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-14.06683</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-75.73526</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1337</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>22296 OLINDA MALDONADO LLOSA</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-14.05958</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-75.74524</v>
-      </c>
-      <c r="I12" t="n">
-        <v>360</v>
-      </c>
-      <c r="J12" t="n">
-        <v>15</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-14.05958</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-75.74524</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>22302 MARIA REICHE NEWMAN</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-14.05981</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-75.74388999999999</v>
-      </c>
-      <c r="I13" t="n">
-        <v>366</v>
-      </c>
-      <c r="J13" t="n">
-        <v>17</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-14.05981</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-75.74389</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>22494 JUAN XXIII</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-14.06554</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-75.72802</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1093</v>
-      </c>
-      <c r="J14" t="n">
-        <v>37</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-14.06554</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-75.72802</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>22521 FRANCISCO FLORES CHINARRO</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-14.0857</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-75.72547</v>
-      </c>
-      <c r="I15" t="n">
-        <v>710</v>
-      </c>
-      <c r="J15" t="n">
-        <v>37</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-14.0857</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-75.72547</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>22533 ANTONIA MORENO DE CACERES</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-14.07882</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-75.73412</v>
-      </c>
-      <c r="I16" t="n">
-        <v>560</v>
-      </c>
-      <c r="J16" t="n">
-        <v>24</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-14.07882</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-75.73412</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>22570</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-14.05231</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-75.73690999999999</v>
-      </c>
-      <c r="I17" t="n">
-        <v>439</v>
-      </c>
-      <c r="J17" t="n">
-        <v>20</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-14.05231</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-75.73691</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>439</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>22626 SAN ANTONIO DE PADUA</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-14.08773</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-75.72958</v>
-      </c>
-      <c r="I18" t="n">
-        <v>424</v>
-      </c>
-      <c r="J18" t="n">
-        <v>23</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-14.08773</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-75.72958</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>JOSE TORIBIO POLO</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-14.08415</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-75.73087</v>
-      </c>
-      <c r="I19" t="n">
-        <v>843</v>
-      </c>
-      <c r="J19" t="n">
-        <v>66</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-14.08415</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-75.73087</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>843</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>22733 REPUBLICA DE CANADA / 514</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-14.05396</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-75.7419</v>
-      </c>
-      <c r="I20" t="n">
-        <v>524</v>
-      </c>
-      <c r="J20" t="n">
-        <v>21</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-14.05396</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-75.7419</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>23007 JUDITH AYBAR DE GRANADOS</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-14.05923</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-75.73038</v>
-      </c>
-      <c r="I21" t="n">
-        <v>825</v>
-      </c>
-      <c r="J21" t="n">
-        <v>32</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-14.05923</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-75.73038</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>150 / 23009</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-14.06516</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-75.73451</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1276</v>
-      </c>
-      <c r="J22" t="n">
-        <v>44</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-14.06516</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-75.73451</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1276</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>23008 EZEQUIEL SANCHEZ GUERRERO</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-14.05978</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-75.72976</v>
-      </c>
-      <c r="I23" t="n">
-        <v>868</v>
-      </c>
-      <c r="J23" t="n">
-        <v>39</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-14.05978</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-75.72976</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>868</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>FERMIN TANGUIS</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-14.05047</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-75.74572000000001</v>
-      </c>
-      <c r="I24" t="n">
-        <v>887</v>
-      </c>
-      <c r="J24" t="n">
-        <v>58</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-14.05047</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-75.74572</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>JOSE DE LA TORRE UGARTE</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-14.07674</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-75.72169</v>
-      </c>
-      <c r="I25" t="n">
-        <v>785</v>
-      </c>
-      <c r="J25" t="n">
-        <v>38</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-14.07674</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-75.72169</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>785</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>MARGARITA SANTA ANA DE BENAVIDES</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-14.068723</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-75.72618799999999</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1268</v>
-      </c>
-      <c r="J26" t="n">
-        <v>60</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-14.068723</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-75.726188</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1268</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-14.065379</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-75.736226</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2114</v>
-      </c>
-      <c r="J27" t="n">
-        <v>126</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-14.065379</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-75.736226</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2114</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>SAN LUIS GONZAGA</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-14.06507</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-75.73309</v>
-      </c>
-      <c r="I28" t="n">
-        <v>2820</v>
-      </c>
-      <c r="J28" t="n">
-        <v>167</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-14.06507</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-75.73309</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2820</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>ANTONIA MORENO DE CACERES</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-14.07652</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-75.73504</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1039</v>
-      </c>
-      <c r="J29" t="n">
-        <v>80</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-14.07652</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-75.73504</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1039</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>89</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-14.08001</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-75.7677</v>
-      </c>
-      <c r="I30" t="n">
-        <v>316</v>
-      </c>
-      <c r="J30" t="n">
-        <v>12</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-14.08001</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-75.7677</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>26</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-14.05915</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-75.73676</v>
-      </c>
-      <c r="I31" t="n">
-        <v>135</v>
-      </c>
-      <c r="J31" t="n">
-        <v>6</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-14.05915</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-75.73676</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>LA INMACULADA</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-14.062905</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-75.729005</v>
-      </c>
-      <c r="I32" t="n">
-        <v>457</v>
-      </c>
-      <c r="J32" t="n">
-        <v>26</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-14.062905</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-75.729005</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>457</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>NEWTON ICA</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-14.065338</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-75.72560300000001</v>
-      </c>
-      <c r="I33" t="n">
-        <v>261</v>
-      </c>
-      <c r="J33" t="n">
-        <v>22</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-14.065338</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-75.725603</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>DE LA CRUZ</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-14.08831</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-75.75127999999999</v>
-      </c>
-      <c r="I34" t="n">
-        <v>642</v>
-      </c>
-      <c r="J34" t="n">
-        <v>68</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-14.08831</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-75.75128</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>SANTA MARIA REYNA</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-14.076653</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-75.72544600000001</v>
-      </c>
-      <c r="I35" t="n">
-        <v>325</v>
-      </c>
-      <c r="J35" t="n">
-        <v>23</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-14.076653</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-75.725446</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>PITAGORAS</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-14.06303</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-75.72998</v>
-      </c>
-      <c r="I36" t="n">
-        <v>358</v>
-      </c>
-      <c r="J36" t="n">
-        <v>29</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-14.06303</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-75.72998</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>SANTA ROSA DE LAS AMERICAS</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-14.066787</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-75.72499500000001</v>
-      </c>
-      <c r="I37" t="n">
-        <v>626</v>
-      </c>
-      <c r="J37" t="n">
-        <v>41</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-14.066787</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-75.724995</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>GEUNICA SCHOOL</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-14.05383</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-75.74883</v>
-      </c>
-      <c r="I38" t="n">
-        <v>342</v>
-      </c>
-      <c r="J38" t="n">
-        <v>23</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-14.05383</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-75.74883</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>PERUANO CANADIENSE</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-14.04574</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-75.75047000000001</v>
-      </c>
-      <c r="I39" t="n">
-        <v>502</v>
-      </c>
-      <c r="J39" t="n">
-        <v>45</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-14.04574</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-75.75047</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>SAN JOSE</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-14.06969</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-75.73130999999999</v>
-      </c>
-      <c r="I40" t="n">
-        <v>679</v>
-      </c>
-      <c r="J40" t="n">
-        <v>50</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-14.06969</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-75.73131</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>UNION AMERICANA</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-14.06628</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-75.72765</v>
-      </c>
-      <c r="I41" t="n">
-        <v>248</v>
-      </c>
-      <c r="J41" t="n">
-        <v>17</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-14.06628</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-75.72765</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>LAS DUNAS</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-14.05366</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-75.74795</v>
-      </c>
-      <c r="I42" t="n">
-        <v>241</v>
-      </c>
-      <c r="J42" t="n">
-        <v>21</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-14.05366</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-75.74795</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>JUAN VALER SANDOVAL</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-14.064225</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-75.726243</v>
-      </c>
-      <c r="I43" t="n">
-        <v>251</v>
-      </c>
-      <c r="J43" t="n">
-        <v>17</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-14.064225</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-75.726243</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>ALAS PERUANAS</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-14.066339</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-75.727245</v>
-      </c>
-      <c r="I44" t="n">
-        <v>478</v>
-      </c>
-      <c r="J44" t="n">
-        <v>41</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-14.066339</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-75.727245</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>TALENTOS MAGISTER</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-14.07439</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-75.72463</v>
-      </c>
-      <c r="I45" t="n">
-        <v>273</v>
-      </c>
-      <c r="J45" t="n">
-        <v>22</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-14.07439</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-75.72463</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>33 CORAZON DEL NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-14.03866</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-75.70053</v>
-      </c>
-      <c r="I46" t="n">
-        <v>367</v>
-      </c>
-      <c r="J46" t="n">
-        <v>17</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-14.03866</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-75.70053</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>22313</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-14.094561</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-75.70219</v>
-      </c>
-      <c r="I47" t="n">
-        <v>555</v>
-      </c>
-      <c r="J47" t="n">
-        <v>22</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-14.094561</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-75.70219</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>22316 IRMA MENDOZA DE CORDOVA</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-14.114687</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-75.692797</v>
-      </c>
-      <c r="I48" t="n">
-        <v>392</v>
-      </c>
-      <c r="J48" t="n">
-        <v>21</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-14.114687</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-75.692797</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>22485 CORONEL FRANCISCO BOLOGNESI CERVANTES</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-14.067564</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-75.68435100000001</v>
-      </c>
-      <c r="I49" t="n">
-        <v>598</v>
-      </c>
-      <c r="J49" t="n">
-        <v>27</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-14.067564</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-75.684351</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>JOSE GREGORIO HUAMAN GIRAO</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-14.093712</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-75.702203</v>
-      </c>
-      <c r="I50" t="n">
-        <v>522</v>
-      </c>
-      <c r="J50" t="n">
-        <v>40</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-14.093712</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-75.702203</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>LOS ANGELES</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-14.092456</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-75.70159</v>
-      </c>
-      <c r="I51" t="n">
-        <v>327</v>
-      </c>
-      <c r="J51" t="n">
-        <v>17</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-14.092456</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-75.70159</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-14.150981</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-75.692846</v>
-      </c>
-      <c r="I52" t="n">
-        <v>588</v>
-      </c>
-      <c r="J52" t="n">
-        <v>32</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-14.150981</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-75.692846</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-14.04704</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-75.69651</v>
-      </c>
-      <c r="I53" t="n">
-        <v>1240</v>
-      </c>
-      <c r="J53" t="n">
-        <v>53</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-14.04704</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-75.69651</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1240</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>VICTOR MANUEL MAURTUA</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-14.04486</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-75.70628000000001</v>
-      </c>
-      <c r="I54" t="n">
-        <v>1457</v>
-      </c>
-      <c r="J54" t="n">
-        <v>63</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-14.04486</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-75.70628</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1457</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>GABINO CHACALTANA HERNANDEZ</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-14.128689</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-75.707508</v>
-      </c>
-      <c r="I55" t="n">
-        <v>683</v>
-      </c>
-      <c r="J55" t="n">
-        <v>40</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-14.128689</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-75.707508</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>04</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-13.98463</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-75.77231</v>
-      </c>
-      <c r="I56" t="n">
-        <v>274</v>
-      </c>
-      <c r="J56" t="n">
-        <v>11</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-13.98463</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-75.77231</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>22328</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-14.000876</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-75.772479</v>
-      </c>
-      <c r="I57" t="n">
-        <v>279</v>
-      </c>
-      <c r="J57" t="n">
-        <v>14</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-14.000876</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-75.772479</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>22340</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-13.971379</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-75.729862</v>
-      </c>
-      <c r="I58" t="n">
-        <v>275</v>
-      </c>
-      <c r="J58" t="n">
-        <v>18</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-13.971379</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-75.729862</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>22346 SAN MARTIN DE PORRAS</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-14.203205</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-75.713542</v>
-      </c>
-      <c r="I59" t="n">
-        <v>1158</v>
-      </c>
-      <c r="J59" t="n">
-        <v>60</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-14.203205</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-75.713542</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1158</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3537,20 +4105,30 @@
           <t>RICARDO PALMA</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>-14.15342</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-75.707131</v>
-      </c>
-      <c r="I60" t="n">
-        <v>388</v>
-      </c>
-      <c r="J60" t="n">
-        <v>16</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-14.15342</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-75.707131</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3589,20 +4167,30 @@
           <t>JESUS MAESTRO</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>-14.06016</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-75.72829</v>
-      </c>
-      <c r="I61" t="n">
-        <v>226</v>
-      </c>
-      <c r="J61" t="n">
-        <v>27</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-14.06016</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-75.72829</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3641,20 +4229,30 @@
           <t>JUAN PABLO II</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>-14.0434</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-75.74196000000001</v>
-      </c>
-      <c r="I62" t="n">
-        <v>23</v>
-      </c>
-      <c r="J62" t="n">
-        <v>3</v>
-      </c>
-      <c r="K62" t="n">
-        <v>1</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-14.0434</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-75.74196</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3693,20 +4291,30 @@
           <t>VIRGEN DEL CARMEN</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>-14.062263</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-75.73137699999999</v>
-      </c>
-      <c r="I63" t="n">
-        <v>274</v>
-      </c>
-      <c r="J63" t="n">
-        <v>34</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-14.062263</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-75.731377</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3745,20 +4353,30 @@
           <t>GENIOMATIC RODAS</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>-14.077928</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-75.725347</v>
-      </c>
-      <c r="I64" t="n">
-        <v>291</v>
-      </c>
-      <c r="J64" t="n">
-        <v>19</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-14.077928</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-75.725347</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3797,20 +4415,30 @@
           <t>JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>-14.08117</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-75.73924</v>
-      </c>
-      <c r="I65" t="n">
-        <v>979</v>
-      </c>
-      <c r="J65" t="n">
-        <v>58</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-14.08117</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-75.73924</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>979</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3849,20 +4477,30 @@
           <t>INTERNACIONAL ELIM</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>-14.06141</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-75.74021</v>
-      </c>
-      <c r="I66" t="n">
-        <v>303</v>
-      </c>
-      <c r="J66" t="n">
-        <v>25</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-14.06141</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-75.74021</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3901,20 +4539,30 @@
           <t>SANTISIMO JESUS</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>-14.08564</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-75.74951</v>
-      </c>
-      <c r="I67" t="n">
-        <v>685</v>
-      </c>
-      <c r="J67" t="n">
-        <v>43</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-14.08564</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-75.74951</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3953,20 +4601,30 @@
           <t>AMISTAD PERUANO JAPONES</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>-14.06167</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-75.73217</v>
-      </c>
-      <c r="I68" t="n">
-        <v>281</v>
-      </c>
-      <c r="J68" t="n">
-        <v>23</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-14.06167</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-75.73217</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -4005,20 +4663,30 @@
           <t>COLOREANDO</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>-14.0666</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-75.73609</v>
-      </c>
-      <c r="I69" t="n">
-        <v>50</v>
-      </c>
-      <c r="J69" t="n">
-        <v>3</v>
-      </c>
-      <c r="K69" t="n">
-        <v>1</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-14.0666</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-75.73609</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -4057,20 +4725,30 @@
           <t>22299 CARLOS CUETO FERNANDINI</t>
         </is>
       </c>
-      <c r="G70" t="n">
-        <v>-14.07166</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-75.72748</v>
-      </c>
-      <c r="I70" t="n">
-        <v>887</v>
-      </c>
-      <c r="J70" t="n">
-        <v>36</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-14.07166</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-75.72748</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -4109,20 +4787,30 @@
           <t>22704 SEÑOR DE LA DIVINA MISERICORDIA</t>
         </is>
       </c>
-      <c r="G71" t="n">
-        <v>-14.04544</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-75.7431</v>
-      </c>
-      <c r="I71" t="n">
-        <v>382</v>
-      </c>
-      <c r="J71" t="n">
-        <v>17</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-14.04544</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-75.7431</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4161,20 +4849,30 @@
           <t>22724 TERESA DE LA CRUZ</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>-14.02998</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-75.737393</v>
-      </c>
-      <c r="I72" t="n">
-        <v>275</v>
-      </c>
-      <c r="J72" t="n">
-        <v>11</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-14.02998</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-75.737393</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4213,20 +4911,30 @@
           <t>22741</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>-14.08024</v>
-      </c>
-      <c r="H73" t="n">
-        <v>-75.76831</v>
-      </c>
-      <c r="I73" t="n">
-        <v>572</v>
-      </c>
-      <c r="J73" t="n">
-        <v>22</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-14.08024</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-75.76831</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -4265,20 +4973,30 @@
           <t>22305 JULIO CESAR TELLO</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>-14.05632</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-75.74841000000001</v>
-      </c>
-      <c r="I74" t="n">
-        <v>1227</v>
-      </c>
-      <c r="J74" t="n">
-        <v>58</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-14.05632</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-75.74841</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1227</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -4317,20 +5035,30 @@
           <t>PAMER ICA</t>
         </is>
       </c>
-      <c r="G75" t="n">
-        <v>-14.07565</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-75.74392</v>
-      </c>
-      <c r="I75" t="n">
-        <v>271</v>
-      </c>
-      <c r="J75" t="n">
-        <v>20</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-14.07565</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-75.74392</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -4369,20 +5097,30 @@
           <t>CARMELITA</t>
         </is>
       </c>
-      <c r="G76" t="n">
-        <v>-14.051407</v>
-      </c>
-      <c r="H76" t="n">
-        <v>-75.75194399999999</v>
-      </c>
-      <c r="I76" t="n">
-        <v>249</v>
-      </c>
-      <c r="J76" t="n">
-        <v>19</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-14.051407</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-75.751944</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -4421,20 +5159,30 @@
           <t>SANTISIMO CRISTO MORENO</t>
         </is>
       </c>
-      <c r="G77" t="n">
-        <v>-14.06744</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-75.73729</v>
-      </c>
-      <c r="I77" t="n">
-        <v>1083</v>
-      </c>
-      <c r="J77" t="n">
-        <v>78</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-14.06744</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-75.73729</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -4473,20 +5221,30 @@
           <t>VIRGEN MARIA DE GUADALUPE</t>
         </is>
       </c>
-      <c r="G78" t="n">
-        <v>-13.98498</v>
-      </c>
-      <c r="H78" t="n">
-        <v>-75.76782</v>
-      </c>
-      <c r="I78" t="n">
-        <v>403</v>
-      </c>
-      <c r="J78" t="n">
-        <v>27</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-13.98498</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-75.76782</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4525,20 +5283,30 @@
           <t>MI PEQUEÑO PARAISO</t>
         </is>
       </c>
-      <c r="G79" t="n">
-        <v>-14.08618</v>
-      </c>
-      <c r="H79" t="n">
-        <v>-75.72346</v>
-      </c>
-      <c r="I79" t="n">
-        <v>81</v>
-      </c>
-      <c r="J79" t="n">
-        <v>9</v>
-      </c>
-      <c r="K79" t="n">
-        <v>1</v>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-14.08618</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-75.72346</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4577,20 +5345,30 @@
           <t>SEÑOR DE LUREN</t>
         </is>
       </c>
-      <c r="G80" t="n">
-        <v>-14.073056</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-75.72703199999999</v>
-      </c>
-      <c r="I80" t="n">
-        <v>527</v>
-      </c>
-      <c r="J80" t="n">
-        <v>53</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-14.073056</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-75.727032</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4629,20 +5407,30 @@
           <t>FAMILY SCHOOL</t>
         </is>
       </c>
-      <c r="G81" t="n">
-        <v>-14.06908</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-75.73603</v>
-      </c>
-      <c r="I81" t="n">
-        <v>89</v>
-      </c>
-      <c r="J81" t="n">
-        <v>14</v>
-      </c>
-      <c r="K81" t="n">
-        <v>1</v>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-14.06908</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-75.73603</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4681,20 +5469,30 @@
           <t>VIRGEN MARIA</t>
         </is>
       </c>
-      <c r="G82" t="n">
-        <v>-14.06875</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-75.72957</v>
-      </c>
-      <c r="I82" t="n">
-        <v>266</v>
-      </c>
-      <c r="J82" t="n">
-        <v>30</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-14.06875</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-75.72957</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4733,20 +5531,30 @@
           <t>DATA SYSTEM'S INGENIEROS</t>
         </is>
       </c>
-      <c r="G83" t="n">
-        <v>-14.08021</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-75.74992</v>
-      </c>
-      <c r="I83" t="n">
-        <v>610</v>
-      </c>
-      <c r="J83" t="n">
-        <v>64</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-14.08021</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-75.74992</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4785,20 +5593,30 @@
           <t>CRISTO MORENO KIDS</t>
         </is>
       </c>
-      <c r="G84" t="n">
-        <v>-14.06725</v>
-      </c>
-      <c r="H84" t="n">
-        <v>-75.73693</v>
-      </c>
-      <c r="I84" t="n">
-        <v>276</v>
-      </c>
-      <c r="J84" t="n">
-        <v>18</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-14.06725</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-75.73693</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4837,20 +5655,30 @@
           <t>SAN IGNACIO SCHOOL</t>
         </is>
       </c>
-      <c r="G85" t="n">
-        <v>-14.10064</v>
-      </c>
-      <c r="H85" t="n">
-        <v>-75.72436999999999</v>
-      </c>
-      <c r="I85" t="n">
-        <v>580</v>
-      </c>
-      <c r="J85" t="n">
-        <v>37</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-14.10064</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-75.72437</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4889,20 +5717,30 @@
           <t>INNOVA SCHOOLS - ICA</t>
         </is>
       </c>
-      <c r="G86" t="n">
-        <v>-14.04917</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-75.75002000000001</v>
-      </c>
-      <c r="I86" t="n">
-        <v>873</v>
-      </c>
-      <c r="J86" t="n">
-        <v>42</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-14.04917</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-75.75002</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>873</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4941,20 +5779,30 @@
           <t>SAN FRANCISCO COLLEGE</t>
         </is>
       </c>
-      <c r="G87" t="n">
-        <v>-14.07832</v>
-      </c>
-      <c r="H87" t="n">
-        <v>-75.75326</v>
-      </c>
-      <c r="I87" t="n">
-        <v>896</v>
-      </c>
-      <c r="J87" t="n">
-        <v>59</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-14.07832</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-75.75326</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4993,20 +5841,30 @@
           <t>EL MEDANO</t>
         </is>
       </c>
-      <c r="G88" t="n">
-        <v>-14.0426</v>
-      </c>
-      <c r="H88" t="n">
-        <v>-75.7564</v>
-      </c>
-      <c r="I88" t="n">
-        <v>309</v>
-      </c>
-      <c r="J88" t="n">
-        <v>17</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-14.0426</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-75.7564</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -5045,20 +5903,30 @@
           <t>22800 COPRODELI SAN FERNANDO</t>
         </is>
       </c>
-      <c r="G89" t="n">
-        <v>-14.06617</v>
-      </c>
-      <c r="H89" t="n">
-        <v>-75.80826</v>
-      </c>
-      <c r="I89" t="n">
-        <v>462</v>
-      </c>
-      <c r="J89" t="n">
-        <v>21</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-14.06617</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-75.80826</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>462</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -5097,20 +5965,30 @@
           <t>EL HUARANGO</t>
         </is>
       </c>
-      <c r="G90" t="n">
-        <v>-14.07727</v>
-      </c>
-      <c r="H90" t="n">
-        <v>-75.76634</v>
-      </c>
-      <c r="I90" t="n">
-        <v>305</v>
-      </c>
-      <c r="J90" t="n">
-        <v>16</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-14.07727</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-75.76634</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -5149,20 +6027,30 @@
           <t>DIVINO NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G91" t="n">
-        <v>-14.07721</v>
-      </c>
-      <c r="H91" t="n">
-        <v>-75.73345</v>
-      </c>
-      <c r="I91" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-14.07721</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-75.73345</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/ICA-ICA-ICA.xlsx
+++ b/ZonasEscolares/excels/ICA-ICA-ICA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>210164</t>
+          <t>210734</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-14.05492</t>
+          <t>-14.07721</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-75.74874</t>
+          <t>-75.73345</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>210197</t>
+          <t>210239</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>05 / JOSE MATIAS MANZANILLA</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-14.06691</t>
+          <t>-14.05375</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-75.72376</t>
+          <t>-75.73603</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>213</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>210215</t>
+          <t>212808</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14 MERCEDES DIBOS DE CAMINO</t>
+          <t>04</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-14.07728</t>
+          <t>-13.98463</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-75.73369</t>
+          <t>-75.77231</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>274</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>210239</t>
+          <t>634436</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22724 TERESA DE LA CRUZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-14.05375</t>
+          <t>-14.02998</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-75.73603</t>
+          <t>-75.737393</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>275</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>210244</t>
+          <t>210767</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>147 / 22495 MICAELA GALINDO ROJAS DE CACERES</t>
+          <t>89</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-14.06688</t>
+          <t>-14.08001</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-75.73694</t>
+          <t>-75.7677</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>316</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>210258</t>
+          <t>210649</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-14.04609</t>
+          <t>-14.065379</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-75.74496</t>
+          <t>-75.736226</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>126</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -873,42 +873,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>210277</t>
+          <t>212851</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>22303 SANTA ROSA DE LIMA</t>
+          <t>22328</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-14.05946</t>
+          <t>-14.000876</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-75.7372</t>
+          <t>-75.772479</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>279</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>210376</t>
+          <t>651505</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>132 SAGRADO CORAZON DEL NIÑO JESUS</t>
+          <t>FAMILY SCHOOL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-14.05933</t>
+          <t>-14.06908</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-75.73022</t>
+          <t>-75.73603</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>89</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>210381</t>
+          <t>210164</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CABO G.C. TEODOSIO ESTEBAN FRANCO GARCIA</t>
+          <t>01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-14.06438</t>
+          <t>-14.05492</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-75.72633</t>
+          <t>-75.74874</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>308</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1059,37 +1059,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>210418</t>
+          <t>210423</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>22295</t>
+          <t>22296 OLINDA MALDONADO LLOSA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-14.06683</t>
+          <t>-14.05958</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-75.73526</t>
+          <t>-75.74524</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>360</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>210423</t>
+          <t>213780</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>22296 OLINDA MALDONADO LLOSA</t>
+          <t>RICARDO PALMA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-14.05958</t>
+          <t>-14.15342</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-75.74524</t>
+          <t>-75.707131</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>388</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>210442</t>
+          <t>848526</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>22302 MARIA REICHE NEWMAN</t>
+          <t>EL HUARANGO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-14.05981</t>
+          <t>-14.07727</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-75.74389</t>
+          <t>-75.76634</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>305</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1245,37 +1245,37 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>210461</t>
+          <t>210654</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>22494 JUAN XXIII</t>
+          <t>SAN LUIS GONZAGA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-14.06554</t>
+          <t>-14.06507</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-75.72802</t>
+          <t>-75.73309</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>167</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>210475</t>
+          <t>210376</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>22521 FRANCISCO FLORES CHINARRO</t>
+          <t>132 SAGRADO CORAZON DEL NIÑO JESUS</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-14.0857</t>
+          <t>-14.05933</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-75.72547</t>
+          <t>-75.73022</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>366</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>210480</t>
+          <t>210442</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>22533 ANTONIA MORENO DE CACERES</t>
+          <t>22302 MARIA REICHE NEWMAN</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-14.07882</t>
+          <t>-14.05981</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-75.73412</t>
+          <t>-75.74389</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>366</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>210499</t>
+          <t>211390</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>22570</t>
+          <t>UNION AMERICANA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-14.05231</t>
+          <t>-14.06628</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-75.73691</t>
+          <t>-75.72765</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>248</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>210507</t>
+          <t>211719</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>22626 SAN ANTONIO DE PADUA</t>
+          <t>JUAN VALER SANDOVAL</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-14.08773</t>
+          <t>-14.064225</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-75.72958</t>
+          <t>-75.726243</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>251</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>210512</t>
+          <t>211823</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JOSE TORIBIO POLO</t>
+          <t>33 CORAZON DEL NIÑO JESUS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-14.08415</t>
+          <t>-14.03866</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-75.73087</t>
+          <t>-75.70053</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>367</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>210550</t>
+          <t>212238</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>22733 REPUBLICA DE CANADA / 514</t>
+          <t>LOS ANGELES</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-14.05396</t>
+          <t>-14.092456</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-75.7419</t>
+          <t>-75.70159</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>327</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>210569</t>
+          <t>634422</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>23007 JUDITH AYBAR DE GRANADOS</t>
+          <t>22704 SEÑOR DE LA DIVINA MISERICORDIA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-14.05923</t>
+          <t>-14.04544</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-75.73038</t>
+          <t>-75.7431</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>382</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>210574</t>
+          <t>801190</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>150 / 23009</t>
+          <t>EL MEDANO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-14.06516</t>
+          <t>-14.0426</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-75.73451</t>
+          <t>-75.7564</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>309</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>210593</t>
+          <t>213191</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>23008 EZEQUIEL SANCHEZ GUERRERO</t>
+          <t>22340</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-14.05978</t>
+          <t>-13.971379</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-75.72976</t>
+          <t>-75.729862</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>275</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>210606</t>
+          <t>738467</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FERMIN TANGUIS</t>
+          <t>CRISTO MORENO KIDS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-14.05047</t>
+          <t>-14.06725</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-75.74572</t>
+          <t>-75.73693</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>276</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>210611</t>
+          <t>563702</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JOSE DE LA TORRE UGARTE</t>
+          <t>GENIOMATIC RODAS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-14.07674</t>
+          <t>-14.077928</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-75.72169</t>
+          <t>-75.725347</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>291</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>210630</t>
+          <t>634554</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MARGARITA SANTA ANA DE BENAVIDES</t>
+          <t>CARMELITA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-14.068723</t>
+          <t>-14.051407</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-75.726188</t>
+          <t>-75.751944</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>249</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>210649</t>
+          <t>210499</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
+          <t>22570</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-14.065379</t>
+          <t>-14.05231</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-75.736226</t>
+          <t>-75.73691</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>439</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,42 +2113,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>210654</t>
+          <t>634506</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SAN LUIS GONZAGA</t>
+          <t>PAMER ICA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-14.06507</t>
+          <t>-14.07565</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-75.73309</t>
+          <t>-75.74392</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>271</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>210705</t>
+          <t>210550</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ANTONIA MORENO DE CACERES</t>
+          <t>22733 REPUBLICA DE CANADA / 514</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-14.07652</t>
+          <t>-14.05396</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-75.73504</t>
+          <t>-75.7419</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>524</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>210767</t>
+          <t>211644</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>LAS DUNAS</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-14.08001</t>
+          <t>-14.05366</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-75.7677</t>
+          <t>-75.74795</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>241</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,37 +2299,37 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>210828</t>
+          <t>212182</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22316 IRMA MENDOZA DE CORDOVA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-14.05915</t>
+          <t>-14.114687</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-75.73676</t>
+          <t>-75.692797</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>392</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>210852</t>
+          <t>815074</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>LA INMACULADA</t>
+          <t>22800 COPRODELI SAN FERNANDO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-14.062905</t>
+          <t>-14.06617</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-75.729005</t>
+          <t>-75.80826</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>462</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>210989</t>
+          <t>211762</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>TALENTOS MAGISTER</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-14.08831</t>
+          <t>-14.07439</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-75.75128</t>
+          <t>-75.72463</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>273</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>211130</t>
+          <t>212120</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SANTA MARIA REYNA</t>
+          <t>22313</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-14.076653</t>
+          <t>-14.094561</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-75.725446</t>
+          <t>-75.70219</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>555</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>211168</t>
+          <t>634455</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PITAGORAS</t>
+          <t>22741</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-14.06303</t>
+          <t>-14.08024</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-75.72998</t>
+          <t>-75.76831</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>572</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>211314</t>
+          <t>210507</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE LAS AMERICAS</t>
+          <t>22626 SAN ANTONIO DE PADUA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-14.066787</t>
+          <t>-14.08773</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-75.724995</t>
+          <t>-75.72958</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>424</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,27 +2733,27 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>211328</t>
+          <t>211130</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>GEUNICA SCHOOL</t>
+          <t>SANTA MARIA REYNA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-14.05383</t>
+          <t>-14.076653</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-75.74883</t>
+          <t>-75.725446</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>325</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>211352</t>
+          <t>211328</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PERUANO CANADIENSE</t>
+          <t>GEUNICA SCHOOL</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-14.04574</t>
+          <t>-14.05383</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-75.75047</t>
+          <t>-75.74883</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>342</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>211366</t>
+          <t>631206</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SAN JOSE</t>
+          <t>AMISTAD PERUANO JAPONES</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-14.06969</t>
+          <t>-14.06167</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-75.73131</t>
+          <t>-75.73217</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>281</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>211390</t>
+          <t>210480</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UNION AMERICANA</t>
+          <t>22533 ANTONIA MORENO DE CACERES</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-14.06628</t>
+          <t>-14.07882</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-75.72765</t>
+          <t>-75.73412</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>560</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>211644</t>
+          <t>576709</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>LAS DUNAS</t>
+          <t>INTERNACIONAL ELIM</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-14.05366</t>
+          <t>-14.06141</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-75.74795</t>
+          <t>-75.74021</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>303</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,37 +3043,37 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>211719</t>
+          <t>210215</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>JUAN VALER SANDOVAL</t>
+          <t>14 MERCEDES DIBOS DE CAMINO</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-14.064225</t>
+          <t>-14.07728</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-75.726243</t>
+          <t>-75.73369</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>533</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>211743</t>
+          <t>210852</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ALAS PERUANAS</t>
+          <t>LA INMACULADA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-14.066339</t>
+          <t>-14.062905</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-75.727245</t>
+          <t>-75.729005</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>457</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>211762</t>
+          <t>212196</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>TALENTOS MAGISTER</t>
+          <t>22485 CORONEL FRANCISCO BOLOGNESI CERVANTES</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-14.07439</t>
+          <t>-14.067564</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-75.72463</t>
+          <t>-75.684351</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>598</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>211823</t>
+          <t>535587</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>33 CORAZON DEL NIÑO JESUS</t>
+          <t>JESUS MAESTRO</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-14.03866</t>
+          <t>-14.06016</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-75.70053</t>
+          <t>-75.72829</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>226</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>212120</t>
+          <t>635049</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>22313</t>
+          <t>VIRGEN MARIA DE GUADALUPE</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-14.094561</t>
+          <t>-13.98498</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-75.70219</t>
+          <t>-75.76782</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>403</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>212182</t>
+          <t>211168</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>22316 IRMA MENDOZA DE CORDOVA</t>
+          <t>PITAGORAS</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-14.114687</t>
+          <t>-14.06303</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-75.692797</t>
+          <t>-75.72998</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>358</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,37 +3415,37 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>212196</t>
+          <t>542291</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>22485 CORONEL FRANCISCO BOLOGNESI CERVANTES</t>
+          <t>JUAN PABLO II</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-14.067564</t>
+          <t>-14.0434</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-75.684351</t>
+          <t>-75.74196</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3477,37 +3477,37 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>212219</t>
+          <t>634120</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>JOSE GREGORIO HUAMAN GIRAO</t>
+          <t>COLOREANDO</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-14.093712</t>
+          <t>-14.0666</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-75.702203</t>
+          <t>-75.73609</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>212238</t>
+          <t>712655</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>LOS ANGELES</t>
+          <t>VIRGEN MARIA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-14.092456</t>
+          <t>-14.06875</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-75.70159</t>
+          <t>-75.72957</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>266</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,42 +3601,42 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>212399</t>
+          <t>210277</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL ROSARIO</t>
+          <t>22303 SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-14.150981</t>
+          <t>-14.05946</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-75.692846</t>
+          <t>-75.7372</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>659</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>212573</t>
+          <t>210197</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>JOSE MARIA ARGUEDAS</t>
+          <t>05 / JOSE MATIAS MANZANILLA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-14.04704</t>
+          <t>-14.06691</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-75.69651</t>
+          <t>-75.72376</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>480</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>212587</t>
+          <t>210569</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>VICTOR MANUEL MAURTUA</t>
+          <t>23007 JUDITH AYBAR DE GRANADOS</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-14.04486</t>
+          <t>-14.05923</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-75.70628</t>
+          <t>-75.73038</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>825</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>212790</t>
+          <t>212399</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>GABINO CHACALTANA HERNANDEZ</t>
+          <t>NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-14.128689</t>
+          <t>-14.150981</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-75.707508</t>
+          <t>-75.692846</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>588</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>212808</t>
+          <t>210244</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>147 / 22495 MICAELA GALINDO ROJAS DE CACERES</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-13.98463</t>
+          <t>-14.06688</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-75.77231</t>
+          <t>-75.73694</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>870</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>212851</t>
+          <t>553557</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>22328</t>
+          <t>VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-14.000876</t>
+          <t>-14.062263</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-75.772479</t>
+          <t>-75.731377</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>274</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>213191</t>
+          <t>634380</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>22340</t>
+          <t>22299 CARLOS CUETO FERNANDINI</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-13.971379</t>
+          <t>-14.07166</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-75.729862</t>
+          <t>-75.72748</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>887</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>213252</t>
+          <t>210461</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>22346 SAN MARTIN DE PORRAS</t>
+          <t>22494 JUAN XXIII</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-14.203205</t>
+          <t>-14.06554</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-75.713542</t>
+          <t>-75.72802</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>213780</t>
+          <t>210475</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>RICARDO PALMA</t>
+          <t>22521 FRANCISCO FLORES CHINARRO</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-14.15342</t>
+          <t>-14.0857</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-75.707131</t>
+          <t>-75.72547</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>710</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>535587</t>
+          <t>738486</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>JESUS MAESTRO</t>
+          <t>SAN IGNACIO SCHOOL</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-14.06016</t>
+          <t>-14.10064</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-75.72829</t>
+          <t>-75.72437</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>580</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,37 +4221,37 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>542291</t>
+          <t>210611</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>JUAN PABLO II</t>
+          <t>JOSE DE LA TORRE UGARTE</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-14.0434</t>
+          <t>-14.07674</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-75.74196</t>
+          <t>-75.72169</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>785</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>553557</t>
+          <t>210593</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>VIRGEN DEL CARMEN</t>
+          <t>23008 EZEQUIEL SANCHEZ GUERRERO</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-14.062263</t>
+          <t>-14.05978</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-75.731377</t>
+          <t>-75.72976</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>868</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>563702</t>
+          <t>212219</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>GENIOMATIC RODAS</t>
+          <t>JOSE GREGORIO HUAMAN GIRAO</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-14.077928</t>
+          <t>-14.093712</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-75.725347</t>
+          <t>-75.702203</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>522</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>576144</t>
+          <t>212790</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>JOSE CARLOS MARIATEGUI</t>
+          <t>GABINO CHACALTANA HERNANDEZ</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-14.08117</t>
+          <t>-14.128689</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-75.73924</t>
+          <t>-75.707508</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>683</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>576709</t>
+          <t>211314</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>INTERNACIONAL ELIM</t>
+          <t>SANTA ROSA DE LAS AMERICAS</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-14.06141</t>
+          <t>-14.066787</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-75.74021</t>
+          <t>-75.724995</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>626</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>608499</t>
+          <t>211743</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SANTISIMO JESUS</t>
+          <t>ALAS PERUANAS</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-14.08564</t>
+          <t>-14.066339</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-75.74951</t>
+          <t>-75.727245</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>478</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>631206</t>
+          <t>779839</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>AMISTAD PERUANO JAPONES</t>
+          <t>INNOVA SCHOOLS - ICA</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-14.06167</t>
+          <t>-14.04917</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-75.73217</t>
+          <t>-75.75002</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>873</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4655,37 +4655,37 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>634120</t>
+          <t>608499</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>COLOREANDO</t>
+          <t>SANTISIMO JESUS</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-14.0666</t>
+          <t>-14.08564</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-75.73609</t>
+          <t>-75.74951</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>685</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>634380</t>
+          <t>210574</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>22299 CARLOS CUETO FERNANDINI</t>
+          <t>150 / 23009</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-14.07166</t>
+          <t>-14.06516</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-75.72748</t>
+          <t>-75.73451</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4779,32 +4779,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>211352</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>22704 SEÑOR DE LA DIVINA MISERICORDIA</t>
+          <t>PERUANO CANADIENSE</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-14.04544</t>
+          <t>-14.04574</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-75.7431</t>
+          <t>-75.75047</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>502</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4841,42 +4841,42 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>634436</t>
+          <t>210418</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>22724 TERESA DE LA CRUZ</t>
+          <t>22295</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-14.02998</t>
+          <t>-14.06683</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-75.737393</t>
+          <t>-75.73526</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4903,32 +4903,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>634455</t>
+          <t>210381</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>22741</t>
+          <t>CABO G.C. TEODOSIO ESTEBAN FRANCO GARCIA</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-14.08024</t>
+          <t>-14.06438</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-75.76831</t>
+          <t>-75.72633</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>949</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>634460</t>
+          <t>211366</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>22305 JULIO CESAR TELLO</t>
+          <t>SAN JOSE</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-14.05632</t>
+          <t>-14.06969</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-75.74841</t>
+          <t>-75.73131</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>679</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>634506</t>
+          <t>212573</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PAMER ICA</t>
+          <t>JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-14.07565</t>
+          <t>-14.04704</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-75.74392</t>
+          <t>-75.69651</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>634554</t>
+          <t>635191</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CARMELITA</t>
+          <t>SEÑOR DE LUREN</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-14.051407</t>
+          <t>-14.073056</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-75.751944</t>
+          <t>-75.727032</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>527</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>634969</t>
+          <t>210606</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SANTISIMO CRISTO MORENO</t>
+          <t>FERMIN TANGUIS</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-14.06744</t>
+          <t>-14.05047</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-75.73729</t>
+          <t>-75.74572</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>887</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>635049</t>
+          <t>576144</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>VIRGEN MARIA DE GUADALUPE</t>
+          <t>JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-13.98498</t>
+          <t>-14.08117</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-75.76782</t>
+          <t>-75.73924</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>979</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5275,42 +5275,42 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>635186</t>
+          <t>634460</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MI PEQUEÑO PARAISO</t>
+          <t>22305 JULIO CESAR TELLO</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-14.08618</t>
+          <t>-14.05632</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-75.72346</t>
+          <t>-75.74841</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>635191</t>
+          <t>783394</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SEÑOR DE LUREN</t>
+          <t>SAN FRANCISCO COLLEGE</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-14.073056</t>
+          <t>-14.07832</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-75.727032</t>
+          <t>-75.75326</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>896</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>651505</t>
+          <t>210828</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>FAMILY SCHOOL</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-14.06908</t>
+          <t>-14.05915</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-75.73603</t>
+          <t>-75.73676</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>135</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>712655</t>
+          <t>210630</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>VIRGEN MARIA</t>
+          <t>MARGARITA SANTA ANA DE BENAVIDES</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-14.06875</t>
+          <t>-14.068723</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-75.72957</t>
+          <t>-75.726188</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>717969</t>
+          <t>213252</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>DATA SYSTEM'S INGENIEROS</t>
+          <t>22346 SAN MARTIN DE PORRAS</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-14.08021</t>
+          <t>-14.203205</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-75.74992</t>
+          <t>-75.713542</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>738467</t>
+          <t>212587</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CRISTO MORENO KIDS</t>
+          <t>VICTOR MANUEL MAURTUA</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-14.06725</t>
+          <t>-14.04486</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-75.73693</t>
+          <t>-75.70628</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>738486</t>
+          <t>717969</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>SAN IGNACIO SCHOOL</t>
+          <t>DATA SYSTEM'S INGENIEROS</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-14.10064</t>
+          <t>-14.08021</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-75.72437</t>
+          <t>-75.74992</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>610</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>779839</t>
+          <t>210512</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - ICA</t>
+          <t>JOSE TORIBIO POLO</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-14.04917</t>
+          <t>-14.08415</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-75.75002</t>
+          <t>-75.73087</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>843</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>783394</t>
+          <t>210989</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO COLLEGE</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-14.07832</t>
+          <t>-14.08831</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-75.75326</t>
+          <t>-75.75128</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>642</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>68</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>801190</t>
+          <t>634969</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>EL MEDANO</t>
+          <t>SANTISIMO CRISTO MORENO</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-14.0426</t>
+          <t>-14.06744</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-75.7564</t>
+          <t>-75.73729</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>78</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5895,32 +5895,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>815074</t>
+          <t>210705</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>22800 COPRODELI SAN FERNANDO</t>
+          <t>ANTONIA MORENO DE CACERES</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-14.06617</t>
+          <t>-14.07652</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-75.80826</t>
+          <t>-75.73504</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5957,32 +5957,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>848526</t>
+          <t>210258</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>EL HUARANGO</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-14.07727</t>
+          <t>-14.04609</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-75.76634</t>
+          <t>-75.74496</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>209</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6019,42 +6019,42 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>210734</t>
+          <t>635186</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>DIVINO NIÑO JESUS</t>
+          <t>MI PEQUEÑO PARAISO</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-14.07721</t>
+          <t>-14.08618</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-75.73345</t>
+          <t>-75.72346</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>81</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/ICA-ICA-ICA.xlsx
+++ b/ZonasEscolares/excels/ICA-ICA-ICA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>210734</t>
+          <t>848526</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DIVINO NIÑO JESUS</t>
+          <t>EL HUARANGO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-14.07721</t>
+          <t>305</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-75.73345</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-14.07727</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-75.76634</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>210239</t>
+          <t>815074</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22800 COPRODELI SAN FERNANDO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-14.05375</t>
+          <t>462</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-75.73603</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>-14.06617</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-75.80826</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>212808</t>
+          <t>801190</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>EL MEDANO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-13.98463</t>
+          <t>309</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-75.77231</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>-14.0426</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-75.7564</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>634436</t>
+          <t>783394</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22724 TERESA DE LA CRUZ</t>
+          <t>SAN FRANCISCO COLLEGE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-14.02998</t>
+          <t>896</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-75.737393</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>-14.07832</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-75.75326</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>210767</t>
+          <t>779839</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>INNOVA SCHOOLS - ICA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-14.08001</t>
+          <t>873</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-75.7677</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>-14.04917</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-75.75002</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>210649</t>
+          <t>738486</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
+          <t>SAN IGNACIO SCHOOL</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-14.065379</t>
+          <t>580</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-75.736226</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>-14.10064</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>-75.72437</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>212851</t>
+          <t>738467</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>22328</t>
+          <t>CRISTO MORENO KIDS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-14.000876</t>
+          <t>276</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-75.772479</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>-14.06725</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-75.73693</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>651505</t>
+          <t>717969</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FAMILY SCHOOL</t>
+          <t>DATA SYSTEM'S INGENIEROS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-14.06908</t>
+          <t>610</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-75.73603</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>-14.08021</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-75.74992</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>210164</t>
+          <t>712655</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>VIRGEN MARIA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-14.05492</t>
+          <t>266</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-75.74874</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>-14.06875</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-75.72957</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,42 +1059,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>210423</t>
+          <t>651505</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>22296 OLINDA MALDONADO LLOSA</t>
+          <t>FAMILY SCHOOL</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-14.05958</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-75.74524</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>-14.06908</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-75.73603</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>213780</t>
+          <t>635191</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>RICARDO PALMA</t>
+          <t>SEÑOR DE LUREN</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-14.15342</t>
+          <t>527</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-75.707131</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>-14.073056</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-75.727032</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,37 +1183,37 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>848526</t>
+          <t>635186</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>EL HUARANGO</t>
+          <t>MI PEQUEÑO PARAISO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-14.07727</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-75.76634</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>-14.08618</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-75.72346</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1245,42 +1245,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>210654</t>
+          <t>635049</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SAN LUIS GONZAGA</t>
+          <t>VIRGEN MARIA DE GUADALUPE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-14.06507</t>
+          <t>403</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-75.73309</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>-13.98498</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>-75.76782</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>210376</t>
+          <t>634969</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>132 SAGRADO CORAZON DEL NIÑO JESUS</t>
+          <t>SANTISIMO CRISTO MORENO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-14.05933</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-75.73022</t>
+          <t>78</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>-14.06744</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-75.73729</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>210442</t>
+          <t>634554</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>22302 MARIA REICHE NEWMAN</t>
+          <t>CARMELITA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-14.05981</t>
+          <t>249</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-75.74389</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>-14.051407</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-75.751944</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>211390</t>
+          <t>634506</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UNION AMERICANA</t>
+          <t>PAMER ICA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-14.06628</t>
+          <t>271</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-75.72765</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>-14.07565</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-75.74392</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>211719</t>
+          <t>634460</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JUAN VALER SANDOVAL</t>
+          <t>22305 JULIO CESAR TELLO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-14.064225</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-75.726243</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>-14.05632</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-75.74841</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>211823</t>
+          <t>634455</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>33 CORAZON DEL NIÑO JESUS</t>
+          <t>22741</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-14.03866</t>
+          <t>572</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-75.70053</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>-14.08024</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-75.76831</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>212238</t>
+          <t>634436</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>LOS ANGELES</t>
+          <t>22724 TERESA DE LA CRUZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-14.092456</t>
+          <t>275</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-75.70159</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>-14.02998</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-75.737393</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1689,22 +1689,22 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>-14.04544</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>-75.7431</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>801190</t>
+          <t>634380</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>EL MEDANO</t>
+          <t>22299 CARLOS CUETO FERNANDINI</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-14.0426</t>
+          <t>887</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-75.7564</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>-14.07166</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-75.72748</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1803,37 +1803,37 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>213191</t>
+          <t>634120</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>22340</t>
+          <t>COLOREANDO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-13.971379</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-75.729862</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>-14.0666</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-75.73609</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>738467</t>
+          <t>631206</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CRISTO MORENO KIDS</t>
+          <t>AMISTAD PERUANO JAPONES</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-14.06725</t>
+          <t>281</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-75.73693</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>-14.06167</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-75.73217</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>563702</t>
+          <t>608499</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>GENIOMATIC RODAS</t>
+          <t>SANTISIMO JESUS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-14.077928</t>
+          <t>685</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-75.725347</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>-14.08564</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-75.74951</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>634554</t>
+          <t>576709</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CARMELITA</t>
+          <t>INTERNACIONAL ELIM</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-14.051407</t>
+          <t>303</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-75.751944</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>-14.06141</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-75.74021</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>210499</t>
+          <t>576144</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>22570</t>
+          <t>JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-14.05231</t>
+          <t>979</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-75.73691</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>-14.08117</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-75.73924</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>634506</t>
+          <t>563702</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PAMER ICA</t>
+          <t>GENIOMATIC RODAS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-14.07565</t>
+          <t>291</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-75.74392</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>-14.077928</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-75.725347</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>210550</t>
+          <t>553557</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>22733 REPUBLICA DE CANADA / 514</t>
+          <t>VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-14.05396</t>
+          <t>274</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-75.7419</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>-14.062263</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-75.731377</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2237,37 +2237,37 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>211644</t>
+          <t>542291</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>LAS DUNAS</t>
+          <t>JUAN PABLO II</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-14.05366</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-75.74795</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>-14.0434</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-75.74196</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>212182</t>
+          <t>535587</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>22316 IRMA MENDOZA DE CORDOVA</t>
+          <t>JESUS MAESTRO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-14.114687</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-75.692797</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>-14.06016</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-75.72829</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>815074</t>
+          <t>213780</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>22800 COPRODELI SAN FERNANDO</t>
+          <t>RICARDO PALMA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-14.06617</t>
+          <t>388</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-75.80826</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>-14.15342</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-75.707131</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>210913</t>
+          <t>213252</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NEWTON ICA</t>
+          <t>22346 SAN MARTIN DE PORRAS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-14.065338</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-75.725603</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>-14.203205</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-75.713542</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>211762</t>
+          <t>213191</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TALENTOS MAGISTER</t>
+          <t>22340</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-14.07439</t>
+          <t>275</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-75.72463</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>-13.971379</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-75.729862</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>212120</t>
+          <t>212851</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>22313</t>
+          <t>22328</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-14.094561</t>
+          <t>279</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-75.70219</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>-14.000876</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-75.772479</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>634455</t>
+          <t>212808</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>22741</t>
+          <t>04</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-14.08024</t>
+          <t>274</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-75.76831</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>-13.98463</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-75.77231</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>210507</t>
+          <t>212790</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>22626 SAN ANTONIO DE PADUA</t>
+          <t>GABINO CHACALTANA HERNANDEZ</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-14.08773</t>
+          <t>683</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-75.72958</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>-14.128689</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-75.707508</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>211130</t>
+          <t>212587</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SANTA MARIA REYNA</t>
+          <t>VICTOR MANUEL MAURTUA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-14.076653</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-75.725446</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>-14.04486</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-75.70628</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>211328</t>
+          <t>212573</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>GEUNICA SCHOOL</t>
+          <t>JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-14.05383</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-75.74883</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>-14.04704</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-75.69651</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>631206</t>
+          <t>212399</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>AMISTAD PERUANO JAPONES</t>
+          <t>NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-14.06167</t>
+          <t>588</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-75.73217</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>-14.150981</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-75.692846</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>210480</t>
+          <t>212238</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>22533 ANTONIA MORENO DE CACERES</t>
+          <t>LOS ANGELES</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-14.07882</t>
+          <t>327</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-75.73412</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>-14.092456</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-75.70159</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>576709</t>
+          <t>212219</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>INTERNACIONAL ELIM</t>
+          <t>JOSE GREGORIO HUAMAN GIRAO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-14.06141</t>
+          <t>522</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-75.74021</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>-14.093712</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-75.702203</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,37 +3043,37 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>210215</t>
+          <t>212196</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>14 MERCEDES DIBOS DE CAMINO</t>
+          <t>22485 CORONEL FRANCISCO BOLOGNESI CERVANTES</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-14.07728</t>
+          <t>598</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-75.73369</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>-14.067564</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-75.684351</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>210852</t>
+          <t>212182</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>LA INMACULADA</t>
+          <t>22316 IRMA MENDOZA DE CORDOVA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-14.062905</t>
+          <t>392</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-75.729005</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>-14.114687</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-75.692797</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>212196</t>
+          <t>212120</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>22485 CORONEL FRANCISCO BOLOGNESI CERVANTES</t>
+          <t>22313</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-14.067564</t>
+          <t>555</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-75.684351</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>-14.094561</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-75.70219</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>535587</t>
+          <t>211823</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>JESUS MAESTRO</t>
+          <t>33 CORAZON DEL NIÑO JESUS</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-14.06016</t>
+          <t>367</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-75.72829</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>-14.03866</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-75.70053</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>635049</t>
+          <t>211762</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>VIRGEN MARIA DE GUADALUPE</t>
+          <t>TALENTOS MAGISTER</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-13.98498</t>
+          <t>273</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-75.76782</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>-14.07439</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-75.72463</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>211168</t>
+          <t>211743</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>PITAGORAS</t>
+          <t>ALAS PERUANAS</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-14.06303</t>
+          <t>478</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-75.72998</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>-14.066339</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-75.727245</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,37 +3415,37 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>542291</t>
+          <t>211719</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>JUAN PABLO II</t>
+          <t>JUAN VALER SANDOVAL</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-14.0434</t>
+          <t>251</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-75.74196</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-14.064225</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-75.726243</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3477,37 +3477,37 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>634120</t>
+          <t>211644</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>COLOREANDO</t>
+          <t>LAS DUNAS</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-14.0666</t>
+          <t>241</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-75.73609</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-14.05366</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-75.74795</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>712655</t>
+          <t>211390</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>VIRGEN MARIA</t>
+          <t>UNION AMERICANA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-14.06875</t>
+          <t>248</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-75.72957</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>-14.06628</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-75.72765</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,42 +3601,42 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>210277</t>
+          <t>211366</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>22303 SANTA ROSA DE LIMA</t>
+          <t>SAN JOSE</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-14.05946</t>
+          <t>679</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-75.7372</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>-14.06969</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-75.73131</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>210197</t>
+          <t>211352</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>05 / JOSE MATIAS MANZANILLA</t>
+          <t>PERUANO CANADIENSE</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-14.06691</t>
+          <t>502</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-75.72376</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>-14.04574</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-75.75047</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>210569</t>
+          <t>211328</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>23007 JUDITH AYBAR DE GRANADOS</t>
+          <t>GEUNICA SCHOOL</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-14.05923</t>
+          <t>342</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-75.73038</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>-14.05383</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-75.74883</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>212399</t>
+          <t>211314</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL ROSARIO</t>
+          <t>SANTA ROSA DE LAS AMERICAS</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-14.150981</t>
+          <t>626</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-75.692846</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>-14.066787</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-75.724995</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>210244</t>
+          <t>211168</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>147 / 22495 MICAELA GALINDO ROJAS DE CACERES</t>
+          <t>PITAGORAS</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-14.06688</t>
+          <t>358</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-75.73694</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>-14.06303</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-75.72998</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>553557</t>
+          <t>211130</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>VIRGEN DEL CARMEN</t>
+          <t>SANTA MARIA REYNA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-14.062263</t>
+          <t>325</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-75.731377</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>-14.076653</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-75.725446</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>634380</t>
+          <t>210989</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>22299 CARLOS CUETO FERNANDINI</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-14.07166</t>
+          <t>642</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-75.72748</t>
+          <t>68</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>-14.08831</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-75.75128</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>210461</t>
+          <t>210913</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>22494 JUAN XXIII</t>
+          <t>NEWTON ICA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-14.06554</t>
+          <t>261</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-75.72802</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>-14.065338</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-75.725603</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>210475</t>
+          <t>210852</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>22521 FRANCISCO FLORES CHINARRO</t>
+          <t>LA INMACULADA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-14.0857</t>
+          <t>457</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-75.72547</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>-14.062905</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-75.729005</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4159,37 +4159,37 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>738486</t>
+          <t>210828</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SAN IGNACIO SCHOOL</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-14.10064</t>
+          <t>135</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-75.72437</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>-14.05915</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-75.73676</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>210611</t>
+          <t>210767</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>JOSE DE LA TORRE UGARTE</t>
+          <t>89</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-14.07674</t>
+          <t>316</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-75.72169</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>-14.08001</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-75.7677</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>210593</t>
+          <t>210734</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>23008 EZEQUIEL SANCHEZ GUERRERO</t>
+          <t>DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-14.05978</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-75.72976</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>-14.07721</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-75.73345</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>212219</t>
+          <t>210705</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>JOSE GREGORIO HUAMAN GIRAO</t>
+          <t>ANTONIA MORENO DE CACERES</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-14.093712</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-75.702203</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>-14.07652</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-75.73504</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,42 +4407,42 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>212790</t>
+          <t>210654</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>GABINO CHACALTANA HERNANDEZ</t>
+          <t>SAN LUIS GONZAGA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-14.128689</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-75.707508</t>
+          <t>167</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>-14.06507</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-75.73309</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>211314</t>
+          <t>210649</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE LAS AMERICAS</t>
+          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-14.066787</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-75.724995</t>
+          <t>126</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>-14.065379</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-75.736226</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>211743</t>
+          <t>210630</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>ALAS PERUANAS</t>
+          <t>MARGARITA SANTA ANA DE BENAVIDES</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-14.066339</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-75.727245</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>-14.068723</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-75.726188</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>779839</t>
+          <t>210611</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - ICA</t>
+          <t>JOSE DE LA TORRE UGARTE</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-14.04917</t>
+          <t>785</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-75.75002</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>-14.07674</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-75.72169</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>608499</t>
+          <t>210606</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SANTISIMO JESUS</t>
+          <t>FERMIN TANGUIS</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-14.08564</t>
+          <t>887</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-75.74951</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>-14.05047</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-75.74572</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>210574</t>
+          <t>210593</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>150 / 23009</t>
+          <t>23008 EZEQUIEL SANCHEZ GUERRERO</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-14.06516</t>
+          <t>868</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-75.73451</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>-14.05978</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-75.72976</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4779,32 +4779,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>211352</t>
+          <t>210574</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>PERUANO CANADIENSE</t>
+          <t>150 / 23009</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-14.04574</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-75.75047</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>-14.06516</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-75.73451</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4841,42 +4841,42 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>210418</t>
+          <t>210569</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>22295</t>
+          <t>23007 JUDITH AYBAR DE GRANADOS</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-14.06683</t>
+          <t>825</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-75.73526</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>-14.05923</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-75.73038</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4903,32 +4903,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>210381</t>
+          <t>210550</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CABO G.C. TEODOSIO ESTEBAN FRANCO GARCIA</t>
+          <t>22733 REPUBLICA DE CANADA / 514</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-14.06438</t>
+          <t>524</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-75.72633</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>-14.05396</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-75.7419</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>211366</t>
+          <t>210512</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SAN JOSE</t>
+          <t>JOSE TORIBIO POLO</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-14.06969</t>
+          <t>843</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-75.73131</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>-14.08415</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-75.73087</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>212573</t>
+          <t>210507</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>JOSE MARIA ARGUEDAS</t>
+          <t>22626 SAN ANTONIO DE PADUA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-14.04704</t>
+          <t>424</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-75.69651</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>-14.08773</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>-75.72958</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>635191</t>
+          <t>210499</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SEÑOR DE LUREN</t>
+          <t>22570</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-14.073056</t>
+          <t>439</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-75.727032</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>-14.05231</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>-75.73691</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>210606</t>
+          <t>210480</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>FERMIN TANGUIS</t>
+          <t>22533 ANTONIA MORENO DE CACERES</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-14.05047</t>
+          <t>560</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-75.74572</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>-14.07882</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-75.73412</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>576144</t>
+          <t>210475</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>JOSE CARLOS MARIATEGUI</t>
+          <t>22521 FRANCISCO FLORES CHINARRO</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-14.08117</t>
+          <t>710</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-75.73924</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>-14.0857</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-75.72547</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5275,32 +5275,32 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>634460</t>
+          <t>210461</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>22305 JULIO CESAR TELLO</t>
+          <t>22494 JUAN XXIII</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-14.05632</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-75.74841</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>-14.06554</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-75.72802</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>783394</t>
+          <t>210442</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO COLLEGE</t>
+          <t>22302 MARIA REICHE NEWMAN</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-14.07832</t>
+          <t>366</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-75.75326</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>-14.05981</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>-75.74389</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5399,42 +5399,42 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>210828</t>
+          <t>210423</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22296 OLINDA MALDONADO LLOSA</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-14.05915</t>
+          <t>360</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-75.73676</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>-14.05958</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-75.74524</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5461,37 +5461,37 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>210630</t>
+          <t>210418</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>MARGARITA SANTA ANA DE BENAVIDES</t>
+          <t>22295</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-14.068723</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-75.726188</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>-14.06683</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>-75.73526</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>213252</t>
+          <t>210381</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>22346 SAN MARTIN DE PORRAS</t>
+          <t>CABO G.C. TEODOSIO ESTEBAN FRANCO GARCIA</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-14.203205</t>
+          <t>949</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-75.713542</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>-14.06438</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>-75.72633</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>212587</t>
+          <t>210376</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>VICTOR MANUEL MAURTUA</t>
+          <t>132 SAGRADO CORAZON DEL NIÑO JESUS</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-14.04486</t>
+          <t>366</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-75.70628</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>-14.05933</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-75.73022</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5647,42 +5647,42 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>717969</t>
+          <t>210277</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>DATA SYSTEM'S INGENIEROS</t>
+          <t>22303 SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-14.08021</t>
+          <t>659</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-75.74992</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>-14.05946</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-75.7372</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>210512</t>
+          <t>210258</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>JOSE TORIBIO POLO</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-14.08415</t>
+          <t>209</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-75.73087</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>-14.04609</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>-75.74496</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>210989</t>
+          <t>210244</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>147 / 22495 MICAELA GALINDO ROJAS DE CACERES</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-14.08831</t>
+          <t>870</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-75.75128</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>-14.06688</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>-75.73694</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5833,32 +5833,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>634969</t>
+          <t>210239</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SANTISIMO CRISTO MORENO</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-14.06744</t>
+          <t>213</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-75.73729</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>-14.05375</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>-75.73603</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5895,37 +5895,37 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>210705</t>
+          <t>210215</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ANTONIA MORENO DE CACERES</t>
+          <t>14 MERCEDES DIBOS DE CAMINO</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-14.07652</t>
+          <t>533</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-75.73504</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>-14.07728</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>-75.73369</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5957,32 +5957,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>210258</t>
+          <t>210197</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>05 / JOSE MATIAS MANZANILLA</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-14.04609</t>
+          <t>480</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-75.74496</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>-14.06691</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-75.72376</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6019,37 +6019,37 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>635186</t>
+          <t>210164</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>MI PEQUEÑO PARAISO</t>
+          <t>01</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-14.08618</t>
+          <t>308</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-75.72346</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>-14.05492</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-75.74874</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">

--- a/ZonasEscolares/excels/ICA-ICA-ICA.xlsx
+++ b/ZonasEscolares/excels/ICA-ICA-ICA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
